--- a/artfynd/A 3100-2024 artfynd.xlsx
+++ b/artfynd/A 3100-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118069998</v>
+        <v>118069587</v>
       </c>
       <c r="B2" t="n">
-        <v>57828</v>
+        <v>100097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663658</v>
+        <v>663669</v>
       </c>
       <c r="R2" t="n">
-        <v>6640443</v>
+        <v>6640440</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118069973</v>
+        <v>118070001</v>
       </c>
       <c r="B3" t="n">
-        <v>57963</v>
+        <v>57656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -835,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663715</v>
+        <v>663713</v>
       </c>
       <c r="R3" t="n">
-        <v>6640427</v>
+        <v>6640716</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118069583</v>
+        <v>118069973</v>
       </c>
       <c r="B4" t="n">
-        <v>97858</v>
+        <v>57963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +904,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663765</v>
+        <v>663715</v>
       </c>
       <c r="R4" t="n">
-        <v>6640688</v>
+        <v>6640427</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118070001</v>
+        <v>118069505</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>100097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,46 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663713</v>
+        <v>663699</v>
       </c>
       <c r="R5" t="n">
-        <v>6640716</v>
+        <v>6640720</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118069587</v>
+        <v>118069586</v>
       </c>
       <c r="B6" t="n">
-        <v>100097</v>
+        <v>97858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663669</v>
+        <v>663762</v>
       </c>
       <c r="R6" t="n">
-        <v>6640440</v>
+        <v>6640592</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069586</v>
+        <v>118069998</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
+        <v>57828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,37 +1219,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663762</v>
+        <v>663658</v>
       </c>
       <c r="R7" t="n">
-        <v>6640592</v>
+        <v>6640443</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118069581</v>
+        <v>118069583</v>
       </c>
       <c r="B8" t="n">
-        <v>100097</v>
+        <v>97858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663775</v>
+        <v>663765</v>
       </c>
       <c r="R8" t="n">
-        <v>6640714</v>
+        <v>6640688</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118069505</v>
+        <v>118070083</v>
       </c>
       <c r="B9" t="n">
-        <v>100097</v>
+        <v>57828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,37 +1432,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663699</v>
+        <v>663654</v>
       </c>
       <c r="R9" t="n">
-        <v>6640720</v>
+        <v>6640445</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118070083</v>
+        <v>118069581</v>
       </c>
       <c r="B10" t="n">
-        <v>57828</v>
+        <v>100097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,46 +1543,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663654</v>
+        <v>663775</v>
       </c>
       <c r="R10" t="n">
-        <v>6640445</v>
+        <v>6640714</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118069584</v>
+        <v>118069585</v>
       </c>
       <c r="B11" t="n">
         <v>97858</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663751</v>
+        <v>663744</v>
       </c>
       <c r="R11" t="n">
-        <v>6640670</v>
+        <v>6640612</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118069585</v>
+        <v>118069584</v>
       </c>
       <c r="B12" t="n">
         <v>97858</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663744</v>
+        <v>663751</v>
       </c>
       <c r="R12" t="n">
-        <v>6640612</v>
+        <v>6640670</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 3100-2024 artfynd.xlsx
+++ b/artfynd/A 3100-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118069587</v>
+        <v>118069998</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
+        <v>57829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663669</v>
+        <v>663658</v>
       </c>
       <c r="R2" t="n">
-        <v>6640440</v>
+        <v>6640443</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118070001</v>
+        <v>118069581</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>100099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,46 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663713</v>
+        <v>663775</v>
       </c>
       <c r="R3" t="n">
-        <v>6640716</v>
+        <v>6640714</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118069973</v>
+        <v>118069586</v>
       </c>
       <c r="B4" t="n">
-        <v>57963</v>
+        <v>97860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,46 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663715</v>
+        <v>663762</v>
       </c>
       <c r="R4" t="n">
-        <v>6640427</v>
+        <v>6640592</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118069505</v>
+        <v>118069584</v>
       </c>
       <c r="B5" t="n">
-        <v>100097</v>
+        <v>97860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663699</v>
+        <v>663751</v>
       </c>
       <c r="R5" t="n">
-        <v>6640720</v>
+        <v>6640670</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118069586</v>
+        <v>118069587</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
+        <v>100099</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663762</v>
+        <v>663669</v>
       </c>
       <c r="R6" t="n">
-        <v>6640592</v>
+        <v>6640440</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069998</v>
+        <v>118069973</v>
       </c>
       <c r="B7" t="n">
-        <v>57828</v>
+        <v>57964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,16 +1210,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1252,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663658</v>
+        <v>663715</v>
       </c>
       <c r="R7" t="n">
-        <v>6640443</v>
+        <v>6640427</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,12 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118069583</v>
+        <v>118069585</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
+        <v>97860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663765</v>
+        <v>663744</v>
       </c>
       <c r="R8" t="n">
-        <v>6640688</v>
+        <v>6640612</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1410,7 @@
         <v>118070083</v>
       </c>
       <c r="B9" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118069581</v>
+        <v>118070001</v>
       </c>
       <c r="B10" t="n">
-        <v>100097</v>
+        <v>57657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,37 +1534,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663775</v>
+        <v>663713</v>
       </c>
       <c r="R10" t="n">
-        <v>6640714</v>
+        <v>6640716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118069585</v>
+        <v>118069505</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
+        <v>100099</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663744</v>
+        <v>663699</v>
       </c>
       <c r="R11" t="n">
-        <v>6640612</v>
+        <v>6640720</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118069584</v>
+        <v>118069583</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
+        <v>97860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663751</v>
+        <v>663765</v>
       </c>
       <c r="R12" t="n">
-        <v>6640670</v>
+        <v>6640688</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 3100-2024 artfynd.xlsx
+++ b/artfynd/A 3100-2024 artfynd.xlsx
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069973</v>
+        <v>118070083</v>
       </c>
       <c r="B7" t="n">
-        <v>57964</v>
+        <v>57829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,16 +1210,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663715</v>
+        <v>663654</v>
       </c>
       <c r="R7" t="n">
-        <v>6640427</v>
+        <v>6640445</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118069585</v>
+        <v>118069973</v>
       </c>
       <c r="B8" t="n">
-        <v>97860</v>
+        <v>57964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,37 +1321,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663744</v>
+        <v>663715</v>
       </c>
       <c r="R8" t="n">
-        <v>6640612</v>
+        <v>6640427</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,12 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118070083</v>
+        <v>118069585</v>
       </c>
       <c r="B9" t="n">
-        <v>57829</v>
+        <v>97860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,46 +1432,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663654</v>
+        <v>663744</v>
       </c>
       <c r="R9" t="n">
-        <v>6640445</v>
+        <v>6640612</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 3100-2024 artfynd.xlsx
+++ b/artfynd/A 3100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118069581</v>
+        <v>118069379</v>
       </c>
       <c r="B2" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663775</v>
+        <v>663601</v>
       </c>
       <c r="R2" t="n">
-        <v>6640714</v>
+        <v>6640424</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118069587</v>
+        <v>117344792</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2682</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Kimsjön, Kimsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663669</v>
+        <v>663800</v>
       </c>
       <c r="R3" t="n">
-        <v>6640440</v>
+        <v>6640677</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,16 +882,11 @@
         <v>118069998</v>
       </c>
       <c r="B4" t="n">
-        <v>57831</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -990,53 +985,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118069586</v>
+        <v>118070083</v>
       </c>
       <c r="B5" t="n">
-        <v>97868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663762</v>
+        <v>663654</v>
       </c>
       <c r="R5" t="n">
-        <v>6640592</v>
+        <v>6640445</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118070083</v>
+        <v>118070004</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,16 +1102,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1141,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663654</v>
+        <v>663857</v>
       </c>
       <c r="R6" t="n">
-        <v>6640445</v>
+        <v>6640802</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1166,17 +1160,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Funbo</t>
+          <t>Rasbo</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118069585</v>
+        <v>118070001</v>
       </c>
       <c r="B7" t="n">
-        <v>97868</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,37 +1208,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663744</v>
+        <v>663713</v>
       </c>
       <c r="R7" t="n">
-        <v>6640612</v>
+        <v>6640716</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1273,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,32 +1303,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118070001</v>
+        <v>81705503</v>
       </c>
       <c r="B8" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1340,24 +1333,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Myskdalen 70,Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663713</v>
+        <v>663691</v>
       </c>
       <c r="R8" t="n">
-        <v>6640716</v>
+        <v>6640491</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1384,12 +1379,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2020-01-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2020-01-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,65 +1409,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Kjell Ljungberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Kjell Ljungberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118069583</v>
+        <v>118069974</v>
       </c>
       <c r="B9" t="n">
-        <v>97868</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663765</v>
+        <v>663686</v>
       </c>
       <c r="R9" t="n">
-        <v>6640688</v>
+        <v>6640380</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,53 +1527,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118069584</v>
+        <v>118070000</v>
       </c>
       <c r="B10" t="n">
-        <v>97868</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663751</v>
+        <v>663683</v>
       </c>
       <c r="R10" t="n">
-        <v>6640670</v>
+        <v>6640382</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,15 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118069505</v>
+        <v>118069973</v>
       </c>
       <c r="B11" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,37 +1644,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Upl</t>
+          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663699</v>
+        <v>663715</v>
       </c>
       <c r="R11" t="n">
-        <v>6640720</v>
+        <v>6640427</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,15 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118069973</v>
+        <v>118069372</v>
       </c>
       <c r="B12" t="n">
-        <v>57966</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,16 +1750,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>208242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1757,27 +1769,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marma-Visteby, Länna, Länna, Almunge, Upl</t>
+          <t>Marma-Visteby, Länna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663715</v>
+        <v>663758</v>
       </c>
       <c r="R12" t="n">
-        <v>6640427</v>
+        <v>6640479</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,6 +1837,1279 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118069367</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>663760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6640623</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118069370</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>663766</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6640521</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118069371</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>663755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6640473</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118069583</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>663765</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6640688</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118069584</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>663751</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6640670</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118069585</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>663744</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6640612</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118069586</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>663762</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6640592</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118069381</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>663611</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6640433</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118069384</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>663602</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6640441</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118069377</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>663629</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6640403</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118069505</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>663699</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6640720</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118069581</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>663775</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6640714</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118069587</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Marma-Visteby, Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>663669</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6640440</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
